--- a/data/nzd0149/nzd0149.xlsx
+++ b/data/nzd0149/nzd0149.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H678"/>
+  <dimension ref="A1:H684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20778,6 +20778,186 @@
         <v>374.15</v>
       </c>
       <c r="H678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>367.75</v>
+      </c>
+      <c r="C679" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="D679" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="E679" t="n">
+        <v>367.39</v>
+      </c>
+      <c r="F679" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="G679" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>367.77</v>
+      </c>
+      <c r="C680" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="D680" t="n">
+        <v>368.09</v>
+      </c>
+      <c r="E680" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="F680" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="G680" t="n">
+        <v>374.9</v>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="C681" t="n">
+        <v>368.35</v>
+      </c>
+      <c r="D681" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="E681" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="F681" t="n">
+        <v>370.49</v>
+      </c>
+      <c r="G681" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>368.67</v>
+      </c>
+      <c r="C682" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="D682" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="E682" t="n">
+        <v>366.84</v>
+      </c>
+      <c r="F682" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="G682" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>368.18</v>
+      </c>
+      <c r="C683" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="D683" t="n">
+        <v>367.68</v>
+      </c>
+      <c r="E683" t="n">
+        <v>366.62</v>
+      </c>
+      <c r="F683" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="G683" t="n">
+        <v>375.02</v>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="C684" t="n">
+        <v>367.97</v>
+      </c>
+      <c r="D684" t="n">
+        <v>367.49</v>
+      </c>
+      <c r="E684" t="n">
+        <v>366.54</v>
+      </c>
+      <c r="F684" t="n">
+        <v>370.2</v>
+      </c>
+      <c r="G684" t="n">
+        <v>374.93</v>
+      </c>
+      <c r="H684" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20794,7 +20974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B704"/>
+  <dimension ref="A1:B710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27837,6 +28017,66 @@
       </c>
       <c r="B704" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -28005,28 +28245,28 @@
         <v>0.1249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003349393880084305</v>
+        <v>0.0007385794744716302</v>
       </c>
       <c r="J2" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K2" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L2" t="n">
-        <v>8.065262024437025e-05</v>
+        <v>3.988116952680087e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.056024036607427</v>
+        <v>2.049696173346243</v>
       </c>
       <c r="N2" t="n">
-        <v>7.769373219400472</v>
+        <v>7.721783022591882</v>
       </c>
       <c r="O2" t="n">
-        <v>2.787359542542094</v>
+        <v>2.778809641301808</v>
       </c>
       <c r="P2" t="n">
-        <v>369.5342915962409</v>
+        <v>369.5622709010026</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28083,28 +28323,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.002615996839047519</v>
+        <v>-0.004900745359212624</v>
       </c>
       <c r="J3" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K3" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L3" t="n">
-        <v>4.675944563814483e-05</v>
+        <v>0.0001669704892656165</v>
       </c>
       <c r="M3" t="n">
-        <v>2.218913380807484</v>
+        <v>2.208913450981227</v>
       </c>
       <c r="N3" t="n">
-        <v>8.175076348800927</v>
+        <v>8.119041809726033</v>
       </c>
       <c r="O3" t="n">
-        <v>2.859209042515242</v>
+        <v>2.849393235361878</v>
       </c>
       <c r="P3" t="n">
-        <v>369.5769973038144</v>
+        <v>369.6014825392299</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28161,28 +28401,28 @@
         <v>0.0609</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09000918093387494</v>
+        <v>-0.08946902205879906</v>
       </c>
       <c r="J4" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K4" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05711374116436219</v>
+        <v>0.05749505129142674</v>
       </c>
       <c r="M4" t="n">
-        <v>2.116859483273837</v>
+        <v>2.101838296980073</v>
       </c>
       <c r="N4" t="n">
-        <v>7.471354893093792</v>
+        <v>7.407834948891306</v>
       </c>
       <c r="O4" t="n">
-        <v>2.733377927234687</v>
+        <v>2.721733813011718</v>
       </c>
       <c r="P4" t="n">
-        <v>370.193524843873</v>
+        <v>370.1877418580548</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28239,28 +28479,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01507659552612206</v>
+        <v>-0.01661611408725324</v>
       </c>
       <c r="J5" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K5" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001996230858947401</v>
+        <v>0.00246794155443264</v>
       </c>
       <c r="M5" t="n">
-        <v>2.036239615127582</v>
+        <v>2.025451335545106</v>
       </c>
       <c r="N5" t="n">
-        <v>6.347972449173772</v>
+        <v>6.300045202418538</v>
       </c>
       <c r="O5" t="n">
-        <v>2.519518297050802</v>
+        <v>2.509989084123383</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2668463638019</v>
+        <v>368.2833516776398</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28317,28 +28557,28 @@
         <v>0.0673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03834275658895758</v>
+        <v>0.0384525529360884</v>
       </c>
       <c r="J6" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K6" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01478976321980352</v>
+        <v>0.0151595830859671</v>
       </c>
       <c r="M6" t="n">
-        <v>1.837908495109131</v>
+        <v>1.822840450095894</v>
       </c>
       <c r="N6" t="n">
-        <v>5.47068121832552</v>
+        <v>5.422776514193324</v>
       </c>
       <c r="O6" t="n">
-        <v>2.338948742132995</v>
+        <v>2.328685576498752</v>
       </c>
       <c r="P6" t="n">
-        <v>369.3051587238418</v>
+        <v>369.3039835460086</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28395,28 +28635,28 @@
         <v>0.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06689150110550739</v>
+        <v>0.06937107080691755</v>
       </c>
       <c r="J7" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="K7" t="n">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03742224921489279</v>
+        <v>0.04077801561946715</v>
       </c>
       <c r="M7" t="n">
-        <v>1.98790636552853</v>
+        <v>1.983381042931316</v>
       </c>
       <c r="N7" t="n">
-        <v>6.429169349367782</v>
+        <v>6.390613843505299</v>
       </c>
       <c r="O7" t="n">
-        <v>2.535580673015115</v>
+        <v>2.527966345405987</v>
       </c>
       <c r="P7" t="n">
-        <v>371.6028642833992</v>
+        <v>371.5762887775101</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28454,7 +28694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H678"/>
+  <dimension ref="A1:H684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56933,6 +57173,258 @@
         </is>
       </c>
     </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>-36.67137085846482,174.74744940786</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>-36.672072539267994,174.74730927510174</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>-36.6727808343644,174.747305549339</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>-36.67348653973731,174.74743774970142</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>-36.67418451429192,174.74763898531444</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>-36.674868990050015,174.7479069692057</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>-36.67137088496407,174.74744962918138</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>-36.672072545796404,174.74730938668523</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>-36.672781128685386,174.74730142599347</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>-36.67348652295159,174.74743785962312</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>-36.67418484669811,174.74763724344064</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>-36.674868187366556,174.74791064033556</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>-36.67137167994137,174.74745626882364</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>-36.672072833046684,174.7473142963582</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>-36.67278090595599,174.74730454636307</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>-36.67348716080863,174.747433682598</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>-36.67418453506731,174.74763887644733</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>-36.674868210974886,174.74791053236117</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>-36.671372077429886,174.74745958864483</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>-36.67207305501267,174.74731809019647</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>-36.67278084231902,174.7473054378972</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>-36.67348746295139,174.74743170400708</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>-36.67418447274115,174.74763920304866</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>-36.67486854149163,174.74790902071945</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>-36.671371428198604,174.74745416627024</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>-36.67207276776255,174.74731318052346</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-36.67278145482468,174.74729685688084</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-36.67348783223695,174.74742928572934</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>-36.67418484669811,174.74763724344064</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>-36.674867904066474,174.74791193602843</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-36.67137105720918,174.74745106777053</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-36.6720725849669,174.7473100561861</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-36.672781605962356,174.74729473948713</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-36.67348796652258,174.7474284063556</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-36.67418513755347,174.74763571930103</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>-36.674868116541525,174.74791096425878</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0149/nzd0149.xlsx
+++ b/data/nzd0149/nzd0149.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H684"/>
+  <dimension ref="A1:H688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20958,6 +20958,126 @@
         <v>374.93</v>
       </c>
       <c r="H684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>367.76</v>
+      </c>
+      <c r="C685" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="D685" t="n">
+        <v>367.6</v>
+      </c>
+      <c r="E685" t="n">
+        <v>366.61</v>
+      </c>
+      <c r="F685" t="n">
+        <v>370.45</v>
+      </c>
+      <c r="G685" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>368.16</v>
+      </c>
+      <c r="C686" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="D686" t="n">
+        <v>367.78</v>
+      </c>
+      <c r="E686" t="n">
+        <v>367.09</v>
+      </c>
+      <c r="F686" t="n">
+        <v>370.58</v>
+      </c>
+      <c r="G686" t="n">
+        <v>375.45</v>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>367.63</v>
+      </c>
+      <c r="C687" t="n">
+        <v>367.45</v>
+      </c>
+      <c r="D687" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="E687" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="F687" t="n">
+        <v>370.76</v>
+      </c>
+      <c r="G687" t="n">
+        <v>376.08</v>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>367</v>
+      </c>
+      <c r="C688" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="D688" t="n">
+        <v>367.27</v>
+      </c>
+      <c r="E688" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="F688" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="G688" t="n">
+        <v>375.57</v>
+      </c>
+      <c r="H688" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20974,7 +21094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B710"/>
+  <dimension ref="A1:B714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28077,6 +28197,46 @@
       </c>
       <c r="B710" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -28245,28 +28405,28 @@
         <v>0.1249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007385794744716302</v>
+        <v>-0.001471545637740316</v>
       </c>
       <c r="J2" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K2" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L2" t="n">
-        <v>3.988116952680087e-06</v>
+        <v>1.598695817606188e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.049696173346243</v>
+        <v>2.047655567403231</v>
       </c>
       <c r="N2" t="n">
-        <v>7.721783022591882</v>
+        <v>7.699480699424194</v>
       </c>
       <c r="O2" t="n">
-        <v>2.778809641301808</v>
+        <v>2.774793812055987</v>
       </c>
       <c r="P2" t="n">
-        <v>369.5622709010026</v>
+        <v>369.5860526937577</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28323,28 +28483,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.004900745359212624</v>
+        <v>-0.007079707697148691</v>
       </c>
       <c r="J3" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K3" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001669704892656165</v>
+        <v>0.0003519115853110044</v>
       </c>
       <c r="M3" t="n">
-        <v>2.208913450981227</v>
+        <v>2.204999516308835</v>
       </c>
       <c r="N3" t="n">
-        <v>8.119041809726033</v>
+        <v>8.093399439553831</v>
       </c>
       <c r="O3" t="n">
-        <v>2.849393235361878</v>
+        <v>2.844890057551228</v>
       </c>
       <c r="P3" t="n">
-        <v>369.6014825392299</v>
+        <v>369.6249282387437</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28401,28 +28561,28 @@
         <v>0.0609</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08946902205879906</v>
+        <v>-0.08974148322789598</v>
       </c>
       <c r="J4" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K4" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05749505129142674</v>
+        <v>0.05851923384300606</v>
       </c>
       <c r="M4" t="n">
-        <v>2.101838296980073</v>
+        <v>2.091137080997629</v>
       </c>
       <c r="N4" t="n">
-        <v>7.407834948891306</v>
+        <v>7.365225570119992</v>
       </c>
       <c r="O4" t="n">
-        <v>2.721733813011718</v>
+        <v>2.713894907714739</v>
       </c>
       <c r="P4" t="n">
-        <v>370.1877418580548</v>
+        <v>370.1906754484609</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28479,28 +28639,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01661611408725324</v>
+        <v>-0.01755723083754572</v>
       </c>
       <c r="J5" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K5" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00246794155443264</v>
+        <v>0.00278792651494042</v>
       </c>
       <c r="M5" t="n">
-        <v>2.025451335545106</v>
+        <v>2.018029840133015</v>
       </c>
       <c r="N5" t="n">
-        <v>6.300045202418538</v>
+        <v>6.267653648868146</v>
       </c>
       <c r="O5" t="n">
-        <v>2.509989084123383</v>
+        <v>2.503528240078019</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2833516776398</v>
+        <v>368.2934742058792</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28557,28 +28717,28 @@
         <v>0.0673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0384525529360884</v>
+        <v>0.0386271264186728</v>
       </c>
       <c r="J6" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K6" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0151595830859671</v>
+        <v>0.01548730730581926</v>
       </c>
       <c r="M6" t="n">
-        <v>1.822840450095894</v>
+        <v>1.813751605510992</v>
       </c>
       <c r="N6" t="n">
-        <v>5.422776514193324</v>
+        <v>5.391591139512819</v>
       </c>
       <c r="O6" t="n">
-        <v>2.328685576498752</v>
+        <v>2.32198000411563</v>
       </c>
       <c r="P6" t="n">
-        <v>369.3039835460086</v>
+        <v>369.3021067013023</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28635,28 +28795,28 @@
         <v>0.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06937107080691755</v>
+        <v>0.07179019292287482</v>
       </c>
       <c r="J7" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K7" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04077801561946715</v>
+        <v>0.04390375944639358</v>
       </c>
       <c r="M7" t="n">
-        <v>1.983381042931316</v>
+        <v>1.984566349909762</v>
       </c>
       <c r="N7" t="n">
-        <v>6.390613843505299</v>
+        <v>6.379944291197226</v>
       </c>
       <c r="O7" t="n">
-        <v>2.527966345405987</v>
+        <v>2.525855160375833</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5762887775101</v>
+        <v>371.5502614944097</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28694,7 +28854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H684"/>
+  <dimension ref="A1:H688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57425,6 +57585,174 @@
         </is>
       </c>
     </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>-36.67137087171444,174.74744951852068</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>-36.672072500097485,174.7473086056009</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-36.67278151846159,174.74729596534664</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-36.67348784902265,174.7474291758076</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>-36.67418461816886,174.74763844097887</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-36.674867455508,174.74791398754212</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>-36.67137140169936,174.74745394494883</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>-36.672072500097485,174.7473086056009</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-36.67278137527853,174.74729797129854</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-36.67348704330867,174.74743445205</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-36.67418434808883,174.7476398562513</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>-36.67486688890775,174.7479165789278</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-36.671370699469314,174.74744807993153</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-36.67207224548908,174.7473042538453</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-36.67278159800774,174.7472948509289</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-36.67348669080874,174.747436760406</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-36.67418397413186,174.74764181585934</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-36.67486540158189,174.747923381315</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-36.67136986474263,174.74744110830736</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-36.67207199740894,174.7473000136732</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-36.67278178096382,174.74729228776812</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-36.67348716080863,174.747433682598</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-36.67418515832886,174.74763561043392</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-36.67486660560761,174.7479178746206</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
